--- a/insurance_forms/039_property_quote_form--insurance_forms.xlsx
+++ b/insurance_forms/039_property_quote_form--insurance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -693,11 +693,7 @@
           <t>Annual property taxes</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Property taxes as a percentage of the estimated value</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -743,11 +739,7 @@
           <t>Annual property maintenance cost</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Property maintenance cost as a percentage of the estimated value</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -831,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other_expenses_1</t>
+          <t>annual_property_tax_rate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other expenses 1</t>
+          <t>Annual property tax rate</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -854,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other_expenses_1_value</t>
+          <t>annual_property_insurance_premium_rate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other expenses 1</t>
+          <t>Annual property insurance premium rate</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -877,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other_expenses_2</t>
+          <t>annual_property_maintenance_cost_rate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other expenses 2</t>
+          <t>Annual property maintenance cost rate</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -900,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>other_expenses_2_value</t>
+          <t>annual_property_management_fee_rate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other expenses 2</t>
+          <t>Annual property management fee rate</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -923,177 +915,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other_expenses_3</t>
+          <t>other_expenses_rate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other expenses 3</t>
+          <t>Other expenses rate</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>other_expenses_3_value</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Other expenses 3</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>other_expenses_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Other expenses 4</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>other_expenses_4_value</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Other expenses 4</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>other_expenses_5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Other expenses 5</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>other_expenses_5_value</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Other expenses 5</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>other_expenses_6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Other expenses 6</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>other_expenses_6_value</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Other expenses 6</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
